--- a/personal_trainer_forms/002_personal_training_consultation_questionnaire--personal_trainer_forms.xlsx
+++ b/personal_trainer_forms/002_personal_training_consultation_questionnaire--personal_trainer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'general_health'}</t>
+          <t>general_health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'General Health'}</t>
+          <t>General Health</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weight_loss'}</t>
+          <t>weight_loss</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weight Loss'}</t>
+          <t>Weight Loss</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'injury_prevention'}</t>
+          <t>injury_prevention</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Injury Prevention'}</t>
+          <t>Injury Prevention</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mother'}</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Mother'}</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'father'}</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Father'}</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'brother/sister'}</t>
+          <t>brother/sister</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Brother/Sister'}</t>
+          <t>Brother/Sister</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'child'}</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Child'}</t>
+          <t>Child</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1x/week'}</t>
+          <t>1x/week</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1x/week'}</t>
+          <t>1x/week</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'2x/week'}</t>
+          <t>2x/week</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '2x/week'}</t>
+          <t>2x/week</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'3x/week'}</t>
+          <t>3x/week</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '3x/week'}</t>
+          <t>3x/week</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'4x/week'}</t>
+          <t>4x/week</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '4x/week'}</t>
+          <t>4x/week</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'5x/week'}</t>
+          <t>5x/week</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '5x/week'}</t>
+          <t>5x/week</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'card'}</t>
+          <t>card</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Card'}</t>
+          <t>Card</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
